--- a/gpu_kernel_performance_45662.xlsx
+++ b/gpu_kernel_performance_45662.xlsx
@@ -480,19 +480,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10.931646</v>
+        <v>10.411949</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1.527631</v>
+        <v>1.550046</v>
       </c>
       <c r="G2" t="n">
         <v>0.923359661</v>
       </c>
       <c r="H2" t="n">
-        <v>0.421078</v>
+        <v>0.437662</v>
       </c>
       <c r="I2" t="n">
         <v>818613159.3600812</v>
@@ -515,19 +515,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.382513</v>
+        <v>11.236559</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.493729</v>
+        <v>1.541259</v>
       </c>
       <c r="G3" t="n">
         <v>0.990344461</v>
       </c>
       <c r="H3" t="n">
-        <v>0.216499</v>
+        <v>0.222997</v>
       </c>
       <c r="I3" t="n">
         <v>890893240.9601057</v>
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.861608</v>
+        <v>10.529774</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1.597971</v>
+        <v>1.625499</v>
       </c>
       <c r="G4" t="n">
         <v>0.958262338</v>
       </c>
       <c r="H4" t="n">
-        <v>0.372228</v>
+        <v>0.37184</v>
       </c>
       <c r="I4" t="n">
         <v>859338262.7201198</v>

--- a/gpu_kernel_performance_45662.xlsx
+++ b/gpu_kernel_performance_45662.xlsx
@@ -480,19 +480,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10.411949</v>
+        <v>10.38699</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1.550046</v>
+        <v>1.533782</v>
       </c>
       <c r="G2" t="n">
         <v>0.923359661</v>
       </c>
       <c r="H2" t="n">
-        <v>0.437662</v>
+        <v>0.421325</v>
       </c>
       <c r="I2" t="n">
         <v>818613159.3600812</v>
@@ -515,19 +515,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.236559</v>
+        <v>11.153248</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.541259</v>
+        <v>1.519443</v>
       </c>
       <c r="G3" t="n">
         <v>0.990344461</v>
       </c>
       <c r="H3" t="n">
-        <v>0.222997</v>
+        <v>0.227374</v>
       </c>
       <c r="I3" t="n">
         <v>890893240.9601057</v>
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.529774</v>
+        <v>10.909962</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1.625499</v>
+        <v>1.539816</v>
       </c>
       <c r="G4" t="n">
         <v>0.958262338</v>
       </c>
       <c r="H4" t="n">
-        <v>0.37184</v>
+        <v>0.370793</v>
       </c>
       <c r="I4" t="n">
         <v>859338262.7201198</v>
